--- a/bht-sjednica-final-review/TD-OUTPUT/3.1 PRILOG II TD - predmjer Sjednica Bileca.xlsx
+++ b/bht-sjednica-final-review/TD-OUTPUT/3.1 PRILOG II TD - predmjer Sjednica Bileca.xlsx
@@ -1374,14 +1374,14 @@
       <c r="B12" s="112" t="inlineStr">
         <is>
           <t>Isporuka i montaža nosive metalne konstrukcije (ground mount support) za prihvat fotonaponskih panela, karakteristika:
- - tip: CUSTOM IZRADA (izvan kataloga zbog opterećenja vjetrom, v. niže) — 3 nosača, svaki za 4 fotonaponska modula (2 reda × 2 kolone, portret); geometrija margina/prepusta preuzeta iz Huawei Standard A-Shaped Support 3.0 konvencije (PVM Tabela 4-20), ali poprečna greda izrađena po mjeri za 2 kolone modula, ne za kataloških 6
- - inklinacija: fiksno 45°, orijentacija JUG (azimut 180°). Nagib je zadržan zbog decembarskog prinosa — pri podnevnoj visini Sunca 23,6° na 42,94° N nagib 45° ostvaruje 93 % direktnog zračenja u odnosu na 85 % pri 35°, a decembar je mjerodavni mjesec za dimenzionisanje autonomnog sistema
- - gabariti PV polja po nosaču (2 reda × 2 modula, portret): širina polja 2305 mm (poprečna greda 2918 mm, bočni prepust 306,5 mm), dužina polja po nagibu 4576 mm (2 × 2278 mm, nepromijenjeno), horizontalna projekcija 3236 mm pri nagibu 45°; donja ivica panela na +0,50 m, gornja ivica na +3,74 m od nivoa terena
- - smještaj: nosači se temelje IZVAN ograđenog platoa, južno od ograde, u pojasu širine cca 1950 mm; odmak od ograde ponuđač utvrđuje pri poziciranju nosača tako da ravan panela nigdje ne dodiruje ogradu; gornja (sjeverna) ivica panela je 1,64 m iznad kote ograde h=2,10 m. Ponuđač provjerava da konstrukcija u cijelosti ostaje unutar zakupljene parcele 16,00 × 9,40 m
- - MJERODAVNO OPTEREĆENJE VJETROM: qp ≥ 1,20 kN/m² (udar 3 s ≈ 45 m/s) prema ovjerenoj projektnoj dokumentaciji lokacije i BAS EN 1991-1-4 sa BiH nacionalnim aneksom, uz primjenu faktora orografije za izloženi planinski vrh na 1076 m n.v. Koeficijent sile cf ≥ 1,5 pri 45° prema EN 1991-1-4 §7.3, osim ako se proračunom dokaže drugačije. Površina izloženosti vjetru 10,55 m² po nosaču (2305 × 4576 mm). Projektne sile po nosaču (GSN, γQ=1,5 / γG,fav=0,9): podizanje ≥18,1 kN, horizontalna sila ≥13,4 kN, moment prevrtanja ≥42,6 kNm. Mjerodavni su podizanje (uplift) i prevrtanje, a ne nosivost tla. NAPOMENA: kataloški nosač tipa A ima deklarisanu otpornost 31 m/s (0,52 kN/m²) pri 45° i 40 m/s (0,87 kN/m²) pri 15°/25°, što je ISPOD opterećenja ovog lokaliteta čak i za manje polje; Ponuđač je stoga dužan ponuditi konstrukciju dimenzionisanu i dokazanu za stvarno opterećenje lokaliteta, uz pisanu potvrdu proizvođača za konkretnu lokaciju (planinski vrh) ako se ipak nudi kataloški proizvod
+ - tip: CUSTOM IZRADA (izvan kataloga zbog opterećenja vjetrom, v. niže) — 4 odvojena nosača u jednom nizu, svaki za 3 fotonaponska modula (3 reda × 1 kolona, položeno); odvojeni nosači umjesto jednog velikog polja smanjuju silu vjetra po konstrukciji (zahtjev Naručioca); geometrija margina/prepusta preuzeta iz Huawei Standard A-Shaped Support 3.0 konvencije (PVM Tabela 4-20), ali poprečna greda izrađena po mjeri za 1 kolonu položenih modula, ne za kataloških 6
+ - inklinacija: fiksno 45°, orijentacija JUGOZAPAD (azimut 225°), niz paralelan sa jugozapadnom ogradom (Naručilac 11.09.2026). Nagib je zadržan zbog decembarskog prinosa — pri podnevnoj visini Sunca 23,6° na 42,94° N nagib 45° ostvaruje 93 % direktnog zračenja u odnosu na 85 % pri 35°, a decembar je mjerodavni mjesec za dimenzionisanje autonomnog sistema
+ - gabariti PV polja po nosaču (3 reda × 1 modul, položeno): širina polja 2278 mm (poprečna greda 2891 mm, bočni prepust 306,5 mm), dužina polja po nagibu 3442 mm (3 × 1134 mm + 2 × 20 mm), horizontalna projekcija 2434 mm pri nagibu 45°; donja ivica panela na +0,50 m, gornja ivica na +2,93 m od nivoa terena; razmak između nosača 400 mm, dužina niza 10 312 mm
+ - smještaj: nosači se temelje IZVAN ograđenog platoa, jugozapadno od ograde (JZ strana), cca 0,40 m od ograde; odmak od ograde ponuđač utvrđuje pri poziciranju nosača tako da ravan panela nigdje ne dodiruje ogradu; gornja (sjeveroistočna) ivica panela je 0,83 m iznad kote ograde h=2,10 m. Ponuđač provjerava da konstrukcija u cijelosti ostaje unutar zakupljene parcele 16,00 × 9,40 m
+ - MJERODAVNO OPTEREĆENJE VJETROM: qp ≥ 1,20 kN/m² (udar 3 s ≈ 45 m/s) prema ovjerenoj projektnoj dokumentaciji lokacije i BAS EN 1991-1-4 sa BiH nacionalnim aneksom, uz primjenu faktora orografije za izloženi planinski vrh na 1076 m n.v. Koeficijent sile cf ≥ 1,5 pri 45° prema EN 1991-1-4 §7.3, osim ako se proračunom dokaže drugačije. Površina izloženosti vjetru 7,84 m² po nosaču (2278 × 3442 mm). Projektne sile po nosaču (GSN, γQ=1,5 / γG,fav=0,9): podizanje ≥13,3 kN, horizontalna sila ≥10,0 kN, moment prevrtanja ≥25,7 kNm. Mjerodavni su podizanje (uplift) i prevrtanje, a ne nosivost tla. NAPOMENA: kataloški nosač tipa A ima deklarisanu otpornost 31 m/s (0,52 kN/m²) pri 45° i 40 m/s (0,87 kN/m²) pri 15°/25°, što je ISPOD opterećenja ovog lokaliteta čak i za manje polje; Ponuđač je stoga dužan ponuditi konstrukciju dimenzionisanu i dokazanu za stvarno opterećenje lokaliteta, uz pisanu potvrdu proizvođača za konkretnu lokaciju (planinski vrh) ako se ipak nudi kataloški proizvod
  - materijal i izrada: konstrukcijski čelik S275JR (S355JR za stubove) prema EN 10025-2, šuplji profili prema EN 10219 — stubovi min. RHS 80×80×4, rigle min. RHS 60×40×3, ili bilo koji presjek za koji se proračunom dokaže najmanje jednak otporni moment; antikorozivna zaštita vrućim cinčanjem prema EN ISO 1461 min. 70 µm lokalno / 85 µm srednje (klasa korozivnosti C4); zavarivanje prema EN 1090-2 klasa izvedbe EXC2; CE označavanje i izjava o svojstvima prema EN 1090-1; konstrukcijski vijci M16 klase 8.8 prema EN 15048, pričvrsni pribor modula A2/A4 nehrđajući
  - spojni pribor: nehrđajući čelik A2/A4
- - uključeno ožičenje i povezivanje panela do PVDB distribucije preko po-string DC odvodnika prenapona (v. crtež E-01): 12 modula se povezuje u DVA STRINGA po 6 modula (string 1 — nosači PV-1 i PV-2; string 2 — nosači PV-2 i PV-3), po jedan string na svaku od dvije rute PVDB ormara</t>
+ - uključeno ožičenje i povezivanje panela do PVDB distribucije preko po-string DC odvodnika prenapona (v. crtež E-01): 12 modula se povezuje u DVA STRINGA po 6 modula (string 1 — nosači PV-1 i PV-2; string 2 — nosači PV-3 i PV-4), po jedan string na svaku od dvije rute PVDB ormara</t>
         </is>
       </c>
       <c r="C12" s="113" t="inlineStr">
@@ -1390,7 +1390,7 @@
         </is>
       </c>
       <c r="D12" s="113" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" s="114" t="n"/>
       <c r="F12" s="114">
@@ -1409,9 +1409,9 @@
           <t>Isporuka i ugradnja sistema sidrenja nosive konstrukcije iz Tačke 1.1 u stijenu/beton, hemijskim (epoksidnim) ankerima.
  - tip: hemijski (epoksidni/vinilesterski) anker M16 ili M20 sa ETA odobrenjem za ugradnju u beton i/ili stijenu, vruće cinčan ili nehrđajući A4
  - broj: najmanje 2 ankera po temeljnoj traci, odnosno 4 ankera po nosaču (minimum 2 po traci zbog redundanse)
- - nosivost: karakteristična sila čupanja ≥30 kN po ankeru; dubina ugradnje prema ETA za konkretnu podlogu. Ukupna projektna sila podizanja po nosaču ≥18,1 kN (GSN); sila po traci od momenta prevrtanja ≥26,6 kN pri razmaku traka 1600 mm
+ - nosivost: karakteristična sila čupanja ≥30 kN po ankeru; dubina ugradnje prema ETA za konkretnu podlogu. Ukupna projektna sila podizanja po nosaču ≥13,3 kN (GSN); sila po traci od momenta prevrtanja ≥16,1 kN pri razmaku traka 1600 mm
  - dokazivanje: ispitivanje čupanjem (pull-out test) na najmanje 10 % ugrađenih ankera, minimalno 2 po nosaču, do 1,5 × projektne sile, uz zapisnik ovjeren od nadzornog organa
- - alternativa: livena U-anker sidra M16, dužine 320 mm, razmaka krakova 180 mm, sa pločama 50×50 mm i dvostrukim maticama, dozvoljena su SAMO uz gravitacioni temelj zapremine ≥0,75 m³ po nosaču (tendovano 0,81 m³ po nosaču, v. Tačku 2.3) — momenat prevrtanja i dalje zahtijeva provjeru lokalnog istezanja trake, ne samo ukupne mase</t>
+ - alternativa: livena U-anker sidra M16, dužine 320 mm, razmaka krakova 180 mm, sa pločama 50×50 mm i dvostrukim maticama, dozvoljena su SAMO uz gravitacioni temelj iz Tačke 2.3 (dvije trake po nosaču, najmanje 0,74 m³ po traci; tendovano 1,053 m³ po traci) — momenat prevrtanja i dalje zahtijeva provjeru lokalnog istezanja trake, ne samo ukupne mase</t>
         </is>
       </c>
       <c r="C13" s="113" t="inlineStr">
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="D13" s="113" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" s="114" t="n"/>
       <c r="F13" s="114">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B15" s="116" t="inlineStr">
         <is>
-          <t>Uzemljenje nosivih konstrukcija: povezivanje sva tri nosača na postojeći prstenasti uzemljivač lokacije bakarnim užetom presjeka 50 mm² sa izolacijom otpornom na UV zračenje i ukopavanje, preko priključnih stezaljki na konstrukciji i bimetalnih (Cu/Fe-Zn) ukrsnih komada radi sprječavanja galvanske korozije. Presjek prema EN 62305-3, Tabela 7, za odvođenje atmosferskog pražnjenja. Kontinuitet svih spojeva ≤0,1 Ω, ukupni otpor uzemljenja ≤10 Ω. DC kablovi se polažu na razmaku ≥0,5 m od odvoda gromobranske instalacije (Huawei §4.1.3).</t>
+          <t>Uzemljenje nosivih konstrukcija: povezivanje sva četiri nosača na postojeći prstenasti uzemljivač lokacije bakarnim užetom presjeka 50 mm² sa izolacijom otpornom na UV zračenje i ukopavanje, preko priključnih stezaljki na konstrukciji i bimetalnih (Cu/Fe-Zn) ukrsnih komada radi sprječavanja galvanske korozije. Presjek prema EN 62305-3, Tabela 7, za odvođenje atmosferskog pražnjenja. Kontinuitet svih spojeva ≤0,1 Ω, ukupni otpor uzemljenja ≤10 Ω. DC kablovi se polažu na razmaku ≥0,5 m od odvoda gromobranske instalacije (Huawei §4.1.3).</t>
         </is>
       </c>
       <c r="C15" s="117" t="inlineStr">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="D15" s="117" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" s="118" t="n"/>
       <c r="F15" s="118">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B20" s="129" t="inlineStr">
         <is>
-          <t>Iskop zemlje/stijene IV-V kategorije za temeljne trake nosača, do donje ivice podložnog betona. Rov širine 550 mm, dubine 950 mm, dužine 3300 mm. 3 nosača × 2 trake × 1,725 m3</t>
+          <t>Iskop zemlje/stijene IV-V kategorije za temeljne trake nosača, do donje ivice podložnog betona. Rov širine 500 mm, dubine 950 mm, dužine 2600 mm. 4 nosača × 2 trake × 1,235 m3</t>
         </is>
       </c>
       <c r="C20" s="130" t="inlineStr">
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="D20" s="130" t="n">
-        <v>10.35</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="E20" s="131" t="n"/>
       <c r="F20" s="131">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="B21" s="132" t="inlineStr">
         <is>
-          <t>Zatrpavanje preostalog dijela rova zemljom od iskopa uz nabijanje u slojevima. Traka je pune dubine, pa se zatrpava samo klin uz kosinu rova. 3 nosača × 2 trake × 0,149 m3</t>
+          <t>Zatrpavanje preostalog dijela rova zemljom od iskopa uz nabijanje u slojevima. Traka je pune dubine, pa se zatrpava samo klin uz kosinu rova. 4 nosača × 2 trake × 0,117 m3</t>
         </is>
       </c>
       <c r="C21" s="130" t="inlineStr">
@@ -1586,7 +1586,7 @@
         </is>
       </c>
       <c r="D21" s="130" t="n">
-        <v>0.89</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E21" s="131" t="n"/>
       <c r="F21" s="131">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="D22" s="130" t="n">
-        <v>9.449999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="E22" s="131" t="n"/>
       <c r="F22" s="131">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="B23" s="129" t="inlineStr">
         <is>
-          <t>Nabavka materijala, transport i ugradnja podložnog betona C12/15 ispod temeljnih traka, prema zahtjevima proizvođača. 3 nosača × 2 trake × 0,091 m3</t>
+          <t>Nabavka materijala, transport i ugradnja podložnog betona C12/15 ispod temeljnih traka, prema zahtjevima proizvođača. 4 nosača × 2 trake × 0,065 m3</t>
         </is>
       </c>
       <c r="C23" s="130" t="inlineStr">
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="D23" s="130" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="E23" s="131" t="n"/>
       <c r="F23" s="131">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="B24" s="129" t="inlineStr">
         <is>
-          <t>Nabavka materijala, transport i betoniranje DVIJE temeljne trake po nosaču, betonom C30/37 klase izloženosti XC4 + XF3 prema BAS EN 206 (aerant 4–6 %, Dmax 16, konzistencija S3), uz upotrebu oplate i njegovanje betona. Armatura B500B, zaštitni sloj ≥50 mm, prema ovjerenom statičkom proračunu iz Tačke 1.3. Obračun po m³ ugrađenog betona. Traka 450 mm (gore) / 550 mm (dolje) × 3300 mm, PUNE dubine 900 mm = 1,485 m³ po traci. 3 nosača × 2 trake × 1,485 m³
+          <t>Nabavka materijala, transport i betoniranje DVIJE temeljne trake po nosaču, betonom C30/37 klase izloženosti XC4 + XF3 prema BAS EN 206 (aerant 4–6 %, Dmax 16, konzistencija S3), uz upotrebu oplate i njegovanje betona. Armatura B500B, zaštitni sloj ≥50 mm, prema ovjerenom statičkom proračunu iz Tačke 1.3. Obračun po m³ ugrađenog betona. Traka 400 mm (gore) / 500 mm (dolje) × 2600 mm, PUNE dubine 900 mm = 1,053 m³ po traci. 4 nosača × 2 trake × 1,053 m³
 BETON I ARMATURA: beton klase C30/37, klase izloženosti XC4 + XF3 prema BAS EN 206, sa aerantom 4–6 %, Dmax 16, konzistencija S3; podložni beton C12/15 d=50 mm; armatura B500B, zaštitni sloj ≥50 mm. Klasa XF3 je mjerodavna zbog cikličnog smrzavanja i odmrzavanja u vlažnom stanju na 1076 m n.v. Temeljna spojnica mora biti ispod dubine smrzavanja za lokalitet, koju Ponuđač navodi u ponudi. Dubina 900 mm je tenderska osnova i mjerodavna je za ponudu; konačnu dubinu i armaturu potvrđuje ovjereni statički proračun iz Tačke 1.3. Traka se betonira punom dubinom rova — vlastita težina trake je dio dokaza sigurnosti na podizanje i prevrtanje.</t>
         </is>
       </c>
@@ -1662,7 +1662,7 @@
         </is>
       </c>
       <c r="D24" s="130" t="n">
-        <v>8.91</v>
+        <v>8.42</v>
       </c>
       <c r="E24" s="131" t="n"/>
       <c r="F24" s="131">
@@ -2150,8 +2150,8 @@
       <c r="B16" s="161" t="inlineStr">
         <is>
           <t>Isporuka i montaža automatskog DEA opisanog pod Tačkom 3.1 u postojeći kontejner, u skid izvedbi, na antivibracionim gumeno-metalnim osloncima (min. 4 kom, vlastita frekvencija ≤8 Hz, statički progib ≥5 mm), postavljenim između skida i roštilja iz Tačke 4.3, sa pripremom za pričvršćenje za podlogu. Stavka obuhvata i nabavnu vrijednost agregata iz Tačke 3.1.
- - PRISTUP: unos kroz kapiju na sredini istočne strane ograde (svijetla širina cca 1,00 m) i ulazna vrata kontejnera 900 × 2000 mm; ponuđač bira način unosa i dužan je u ponudi potvrditi izvodljivost
- - SERVISNI PROSTOR ( prema crtežu M-01): agregat se postavlja CENTRIRANO u slobodnom prostoru kontejnera, sa najmanje 720 mm sa JUŽNE i 720 mm sa SJEVERNE strane (520 mm na dijelu gdje je GRO) te 1155 mm sa ISTOČNE strane. Sa ZAPADNE strane je hladnjak, koji izduvava u kanal kroz zid i ne servisira se s te strane
+ - PRISTUP: unos kroz kapiju na sredini jugoistočne strane ograde (svijetla širina cca 1,00 m) i ulazna vrata kontejnera 900 × 2000 mm; ponuđač bira način unosa i dužan je u ponudi potvrditi izvodljivost
+ - SERVISNI PROSTOR ( prema crtežu M-01): agregat se postavlja CENTRIRANO u slobodnom prostoru kontejnera, sa najmanje 720 mm sa JUGOZAPADNE i 720 mm sa SJEVEROISTOČNE strane (520 mm na dijelu gdje je GRO) te 1155 mm sa JUGOISTOČNE strane. Sa SJEVEROZAPADNE strane je hladnjak, koji izduvava u kanal kroz zid i ne servisira se s te strane
  - dimenzije skida prilagoditi raspoloživom prostoru
  - dozvoljeni nivo buke izvan kontejnera &lt;68 dBA pri opterećenju 75 % na 7 m, režim Standby
  - taster EMERGENCY STOP uz ulazna vrata kontejnera</t>
@@ -2180,7 +2180,7 @@
       <c r="B17" s="161" t="inlineStr">
         <is>
           <t>Isporuka, montaža i povezivanje dvoplašnog spremnika dizel goriva zapremine 500 l (0,5 m³), od čeličnog lima, sa svim spojnim priborom, cjevovodima i armaturama. Zapremina spremnika nije predmet varijantnih rješenja i ne umanjuje se ni u slučaju ojačanja poda iz Tačke 4.3.
- - referentne dimenzije 1050 × 600 × 1310 mm, masa prazan 170 kg (pun ≈590 kg); smještaj u JUGOISTOČNI ugao kontejnera, prema crtežu M-01
+ - referentne dimenzije 1050 × 600 × 1310 mm, masa prazan 170 kg (pun ≈590 kg); smještaj u JUŽNI ugao kontejnera (uz JZ i JI zid), prema crtežu M-01
  - odušna cijev izvedena IZVAN kontejnera, otvor zaštićen metalnom mrežicom; odzračni cjevovod od čeličnih bešavnih cijevi prema DIN 2448 sa odzračnim ventilom tip AT
  - priključak za punjenje sa zatvaračem, izveden na vanjskoj strani kontejnera; obezbijediti prilaz autocisterne, a na pretakalištu ugraditi uređaj za odvođenje statičkog elektriciteta
  - priključak za pražnjenje sa zatvaračem i priključkom za crijevo
@@ -2264,8 +2264,8 @@
       </c>
       <c r="B20" s="161" t="inlineStr">
         <is>
-          <t>Izrada i montaža limenog kanala za odvod toplog zraka sa agregata, od pocinčanog lima d=1 mm, sa prirubnicama 30 × 1,5 mm, komplet sa fazonskim komadima i ovjesnim priborom. Kanal je PRELAZNI KOMAD od prirubnice hladnjaka do žaluzine 600 × 600 mm kroz ZAPADNI zid; hladnjak je 60 mm od zida, pa je razvijena površina ≈1,0 m². Stvarnu mjeru uzeti na licu mjesta prema ponuđenom agregatu.
-RASPORED (OBAVEZNO, prema crtežu M-01): kanal se vodi najkraćim putem od radijatora kroz ZAPADNI zid kontejnera do izlazne žaluzine iz Tačke 4.6.</t>
+          <t>Izrada i montaža limenog kanala za odvod toplog zraka sa agregata, od pocinčanog lima d=1 mm, sa prirubnicama 30 × 1,5 mm, komplet sa fazonskim komadima i ovjesnim priborom. Kanal je PRELAZNI KOMAD od prirubnice hladnjaka do žaluzine 600 × 600 mm kroz SJEVEROZAPADNI (SZ) zid; hladnjak je 60 mm od zida, pa je razvijena površina ≈1,0 m². Stvarnu mjeru uzeti na licu mjesta prema ponuđenom agregatu.
+RASPORED (OBAVEZNO, prema crtežu M-01): kanal se vodi najkraćim putem od radijatora kroz SJEVEROZAPADNI (SZ) zid kontejnera do izlazne žaluzine iz Tačke 4.6.</t>
         </is>
       </c>
       <c r="C20" s="128" t="inlineStr">
@@ -2291,7 +2291,7 @@
       <c r="B21" s="161" t="inlineStr">
         <is>
           <t>Isporuka i montaža fiksne žaluzine na kraju kanala za odvod toplog zraka, dimenzija 600 × 600 mm, sa zaštitnom mrežicom, komplet sa montažnim materijalom.
-RASPORED (OBAVEZNO, prema crtežu M-01): žaluzina se ugrađuje u ZAPADNI zid kontejnera, na osi radijatora agregata. Topli zrak i izduv se NE smiju izbacivati prema SJEVERNOJ strani, gdje se nalaze postojeći vanjski ormari ICC360-HA1-C1 i MTS9302A i gdje se nalazi usis svježeg zraka.</t>
+RASPORED (OBAVEZNO, prema crtežu M-01): žaluzina se ugrađuje u SJEVEROZAPADNI (SZ) zid kontejnera, na osi radijatora agregata. Topli zrak i izduv se NE smiju izbacivati prema SJEVEROISTOČNOJ (SI) strani, gdje se nalaze postojeći vanjski ormari ICC360-HA1-C1 i MTS9302A i gdje se nalazi usis svježeg zraka.</t>
         </is>
       </c>
       <c r="C21" s="128" t="inlineStr">
@@ -2317,7 +2317,7 @@
       <c r="B22" s="161" t="inlineStr">
         <is>
           <t>Isporuka i montaža vanjske fiksne žaluzine za dovod svježeg zraka, dimenzija 500 × 700 mm, sa zaštitnom mrežicom. Žaluzine postaviti tako da se spriječi ulaz vode u kontejner prilikom padavina.
-RASPORED (OBAVEZNO, prema crtežu M-01): žaluzina se ugrađuje u SJEVERNI zid kontejnera, na istočnom kraju, sa donjom ivicom na cca 0,30 m od poda. Sjeverna strana je zasjenjena i daje najhladniji usisni zrak, čime se poboljšava hlađenje agregata. Žaluzina se postavlja istočno od vanjskih ormara ICC360-HA1-C1/MTS9302A kako se ne bi usisavao topli zrak sa njih. Prostorna udaljenost od izduva i od odušne cijevi spremnika ≥3 m. Nije dozvoljeno izvesti dovod zraka kroz ulazna vrata.</t>
+RASPORED (OBAVEZNO, prema crtežu M-01): žaluzina se ugrađuje u SJEVEROISTOČNI (SI) zid kontejnera, na jugoistočnom kraju, sa donjom ivicom na cca 0,30 m od poda. Sjeveroistočna strana je zasjenjena veći dio dana i daje najhladniji usisni zrak, čime se poboljšava hlađenje agregata. Žaluzina se postavlja jugoistočno od vanjskih ormara ICC360-HA1-C1/MTS9302A kako se ne bi usisavao topli zrak sa njih. Prostorna udaljenost od izduva i od odušne cijevi spremnika ≥3 m. Nije dozvoljeno izvesti dovod zraka kroz ulazna vrata.</t>
         </is>
       </c>
       <c r="C22" s="128" t="inlineStr">
@@ -2343,7 +2343,7 @@
       <c r="B23" s="161" t="inlineStr">
         <is>
           <t>Isporuka i montaža aksijalnog EC ventilatora 48 V DC za prinudnu ventilaciju prostora agregata, kapaciteta 1200 m³/h, Ø315 mm, napajanog iz DC razvoda −48 V (Tačka 5.16), sa termostatskim upravljanjem. Ventilator radi prema termostatu dok agregat miruje; za vrijeme rada agregata kontroler agregata ga isključuje. Minimalna potrebna ventilacija prostora iznosi 120 m³/h (6 izmjena zraka na sat).
-RASPORED (prema crtežu M-01): ventilator se ugrađuje u ISTOČNI zid kontejnera, u gornjoj zoni (donja ivica cca 1,75 m), sjeverno od ulaznih vrata.</t>
+RASPORED (prema crtežu M-01): ventilator se ugrađuje u JUGOISTOČNI (JI) zid kontejnera, u gornjoj zoni (donja ivica cca 1,75 m), sjeveroistočno od ulaznih vrata.</t>
         </is>
       </c>
       <c r="C23" s="128" t="inlineStr">
@@ -2394,7 +2394,7 @@
       <c r="B25" s="161" t="inlineStr">
         <is>
           <t>Isporuka i montaža sistema za odvod izduvnih gasova: čelična cijev NO 50 mm sa ispušnim loncem (prigušivačem), izvedena izvan kontejnera i završena IZNAD KROVA, usmjereno naviše, sa kapom protiv upada padavina. Na kraju izduvne cijevi postaviti HVATAČ ISKRI. Dužine: od elastičnog umetka do prigušivača, sa jednim lukom 90°, 1 m; od prigušivača do izlaza iznad krova, do 4 m. Komplet sa elastičnim umetkom, lukovima i montažnim materijalom.
-TRASA: fleksibilni spoj i prigušivač neposredno iza motora, uspon uz ZAPADNI zid kontejnera, završetak IZNAD KROVA usmjeren naviše, sa hvatačem iskri.
+TRASA: fleksibilni spoj i prigušivač neposredno iza motora, uspon uz SJEVEROZAPADNI (SZ) zid kontejnera, završetak IZNAD KROVA usmjeren naviše, sa hvatačem iskri.
 NO 50: sa agregatom 18 kVA protok izduvnih gasova je 192 m³/h pri 413 °C, brzina 27,2 m/s (ispod uobičajenih 30 m/s), protutlak ≈1,9 kPa uz dozvoljenih 10,2 kPa.</t>
         </is>
       </c>

--- a/bht-sjednica-final-review/TD-OUTPUT/3.1 PRILOG II TD - predmjer Sjednica Bileca.xlsx
+++ b/bht-sjednica-final-review/TD-OUTPUT/3.1 PRILOG II TD - predmjer Sjednica Bileca.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOT 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOT 2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="LOT 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="LOT 2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -1225,7 +1225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5.71" customWidth="1" style="91" min="1" max="1"/>
@@ -1378,10 +1378,11 @@
  - inklinacija: fiksno 45°, orijentacija JUGOZAPAD (azimut 225°), niz paralelan sa jugozapadnom ogradom (Naručilac 11.09.2026). Nagib je zadržan zbog decembarskog prinosa — pri podnevnoj visini Sunca 23,6° na 42,94° N nagib 45° ostvaruje 93 % direktnog zračenja u odnosu na 85 % pri 35°, a decembar je mjerodavni mjesec za dimenzionisanje autonomnog sistema
  - gabariti PV polja po nosaču (3 reda × 1 modul, položeno): širina polja 2278 mm (poprečna greda 2891 mm, bočni prepust 306,5 mm), dužina polja po nagibu 3442 mm (3 × 1134 mm + 2 × 20 mm), horizontalna projekcija 2434 mm pri nagibu 45°; donja ivica panela na +0,50 m, gornja ivica na +2,93 m od nivoa terena; razmak između nosača 400 mm, dužina niza 10 312 mm
  - smještaj: nosači se temelje IZVAN ograđenog platoa, jugozapadno od ograde (JZ strana), cca 0,40 m od ograde; odmak od ograde ponuđač utvrđuje pri poziciranju nosača tako da ravan panela nigdje ne dodiruje ogradu; gornja (sjeveroistočna) ivica panela je 0,83 m iznad kote ograde h=2,10 m. Ponuđač provjerava da konstrukcija u cijelosti ostaje unutar zakupljene parcele 16,00 × 9,40 m
- - MJERODAVNO OPTEREĆENJE VJETROM: qp ≥ 1,20 kN/m² (udar 3 s ≈ 45 m/s) prema ovjerenoj projektnoj dokumentaciji lokacije i BAS EN 1991-1-4 sa BiH nacionalnim aneksom, uz primjenu faktora orografije za izloženi planinski vrh na 1076 m n.v. Koeficijent sile cf ≥ 1,5 pri 45° prema EN 1991-1-4 §7.3, osim ako se proračunom dokaže drugačije. Površina izloženosti vjetru 7,84 m² po nosaču (2278 × 3442 mm). Projektne sile po nosaču (GSN, γQ=1,5 / γG,fav=0,9): podizanje ≥13,3 kN, horizontalna sila ≥10,0 kN, moment prevrtanja ≥25,7 kNm. Mjerodavni su podizanje (uplift) i prevrtanje, a ne nosivost tla. NAPOMENA: kataloški nosač tipa A ima deklarisanu otpornost 31 m/s (0,52 kN/m²) pri 45° i 40 m/s (0,87 kN/m²) pri 15°/25°, što je ISPOD opterećenja ovog lokaliteta čak i za manje polje; Ponuđač je stoga dužan ponuditi konstrukciju dimenzionisanu i dokazanu za stvarno opterećenje lokaliteta, uz pisanu potvrdu proizvođača za konkretnu lokaciju (planinski vrh) ako se ipak nudi kataloški proizvod
+ - MJERODAVNO OPTEREĆENJE VJETROM: qp ≥ 1,20 kN/m² (udar 3 s ≈ 45 m/s) prema ovjerenoj projektnoj dokumentaciji lokacije i BAS EN 1991-1-4 sa BiH nacionalnim aneksom, uz primjenu faktora orografije za izloženi planinski vrh na 1076 m n.v. Koeficijent sile cf ≥ 1,5 pri 45° prema EN 1991-1-4 §7.3, osim ako se proračunom dokaže drugačije. Površina izloženosti vjetru 7,84 m² po nosaču (2278 × 3442 mm). Projektne sile po nosaču (podizanje, horizontalna sila, moment prevrtanja) proizlaze iz koncepta konstrukcije koji Ponuđač nudi; Ponuđač ih iskazuje i dokazuje u tehničkom rješenju i statičkom proračunu iz Tačke 1.3. Mjerodavni su podizanje (uplift) i prevrtanje, a ne nosivost tla. NAPOMENA: kataloški nosač tipa A ima deklarisanu otpornost 31 m/s (0,52 kN/m²) pri 45° i 40 m/s (0,87 kN/m²) pri 15°/25°, što je ISPOD opterećenja ovog lokaliteta čak i za manje polje; Ponuđač je stoga dužan ponuditi konstrukciju dimenzionisanu i dokazanu za stvarno opterećenje lokaliteta, uz pisanu potvrdu proizvođača za konkretnu lokaciju (planinski vrh) ako se ipak nudi kataloški proizvod
  - materijal i izrada: konstrukcijski čelik S275JR (S355JR za stubove) prema EN 10025-2, šuplji profili prema EN 10219 — stubovi min. RHS 80×80×4, rigle min. RHS 60×40×3, ili bilo koji presjek za koji se proračunom dokaže najmanje jednak otporni moment; antikorozivna zaštita vrućim cinčanjem prema EN ISO 1461 min. 70 µm lokalno / 85 µm srednje (klasa korozivnosti C4); zavarivanje prema EN 1090-2 klasa izvedbe EXC2; CE označavanje i izjava o svojstvima prema EN 1090-1; konstrukcijski vijci M16 klase 8.8 prema EN 15048, pričvrsni pribor modula A2/A4 nehrđajući
  - spojni pribor: nehrđajući čelik A2/A4
- - uključeno ožičenje i povezivanje panela do PVDB distribucije preko po-string DC odvodnika prenapona (v. crtež E-01): 12 modula se povezuje u DVA STRINGA po 6 modula (string 1 — nosači PV-1 i PV-2; string 2 — nosači PV-3 i PV-4), po jedan string na svaku od dvije rute PVDB ormara</t>
+ - uključeno ožičenje i povezivanje panela do PVDB distribucije preko po-string DC odvodnika prenapona (v. crtež E-01): 12 modula se povezuje u DVA STRINGA po 6 modula (string 1 — nosači PV-1 i PV-2; string 2 — nosači PV-3 i PV-4), po jedan string na svaku od dvije rute PVDB ormara
+ - UZ PONUDU: Ponuđač je obavezan da uz ponudu dostavi tehničko rješenje konstrukcije za prihvat fotonaponskih panela za predmetnu lokaciju, sa obaveznim statičkim proračunom (Tačka 1.3) i specifikacijom materijala. Tehničko rješenje mora biti pregledano i odobreno prije početka izvođenja radova</t>
         </is>
       </c>
       <c r="C12" s="113" t="inlineStr">
@@ -1409,9 +1410,9 @@
           <t>Isporuka i ugradnja sistema sidrenja nosive konstrukcije iz Tačke 1.1 u stijenu/beton, hemijskim (epoksidnim) ankerima.
  - tip: hemijski (epoksidni/vinilesterski) anker M16 ili M20 sa ETA odobrenjem za ugradnju u beton i/ili stijenu, vruće cinčan ili nehrđajući A4
  - broj: najmanje 2 ankera po temeljnoj traci, odnosno 4 ankera po nosaču (minimum 2 po traci zbog redundanse)
- - nosivost: karakteristična sila čupanja ≥30 kN po ankeru; dubina ugradnje prema ETA za konkretnu podlogu. Ukupna projektna sila podizanja po nosaču ≥13,3 kN (GSN); sila po traci od momenta prevrtanja ≥16,1 kN pri razmaku traka 1600 mm
+ - nosivost i dubina ugradnje: prema ETA za konkretnu podlogu i prema statičkom proračunu iz Tačke 1.3; projektne sile ankerisanja proizlaze iz koncepta konstrukcije koji Ponuđač nudi i iskazuju se u tehničkom rješenju
  - dokazivanje: ispitivanje čupanjem (pull-out test) na najmanje 10 % ugrađenih ankera, minimalno 2 po nosaču, do 1,5 × projektne sile, uz zapisnik ovjeren od nadzornog organa
- - alternativa: livena U-anker sidra M16, dužine 320 mm, razmaka krakova 180 mm, sa pločama 50×50 mm i dvostrukim maticama, dozvoljena su SAMO uz gravitacioni temelj iz Tačke 2.3 (dvije trake po nosaču, najmanje 0,74 m³ po traci; tendovano 1,053 m³ po traci) — momenat prevrtanja i dalje zahtijeva provjeru lokalnog istezanja trake, ne samo ukupne mase</t>
+ - alternativa: livena U-anker sidra M16, dužine 320 mm, razmaka krakova 180 mm, sa pločama 50×50 mm i dvostrukim maticama, dozvoljena su SAMO uz gravitacioni temelj iz Tačke 2.4 (dvije trake po nosaču, tendovano 1,170 m³ po traci) — dovoljnost vlastite težine i lokalno istezanje trake dokazuju se statičkim proračunom iz Tačke 1.3</t>
         </is>
       </c>
       <c r="C13" s="113" t="inlineStr">
@@ -1437,11 +1438,12 @@
       <c r="B14" s="116" t="inlineStr">
         <is>
           <t>Statički proračun nosive konstrukcije i temelja, ovjeren i potpisan od strane ovlaštenog inženjera.
- - dokaz otpornosti na pritisak vjetra qp ≥ 1,20 kN/m² pri nagibu 45°, prema BAS EN 1991-1-4 sa BiH nacionalnim aneksom, uključujući orografiju
+ - dokaz na dejstvo vjetra prema BAS EN 1991-1-4 sa BiH nacionalnim aneksom, uključujući faktor orografije za lokalitet
  - dokaz na opterećenje snijegom prema BAS EN 1991-1-3 i na radijalni led 20 mm gustine 300 kg/m³
- - dokaz sigurnosti na podizanje (uplift) i prevrtanje prema EN 1990 (γQ,dst = 1,5; γG,stb = 0,9)
+ - dokaz sigurnosti na podizanje (uplift) i prevrtanje prema BAS EN 1990
+ - dimenzionisanje čelične konstrukcije prema BAS EN 1993-1-1, izvedba prema BAS EN 1090-2
  - dimenzionisanje temelja i sidrenja prema stvarnim geotehničkim uslovima (kamenito tlo), uz navođenje dubine smrzavanja za lokalitet
-NAPOMENA: proračun se dostavlja tokom realizacije kao uslov za primopredaju.</t>
+NAPOMENA: Statički proračun se dostavlja u sklopu tehničkog rješenja i uslov je za počinjanje radova. Prije početka izvođenja radova tehničko rješenje mora biti pregledano i odobreno.</t>
         </is>
       </c>
       <c r="C14" s="117" t="inlineStr">
@@ -1552,7 +1554,7 @@
       </c>
       <c r="B20" s="129" t="inlineStr">
         <is>
-          <t>Iskop zemlje/stijene IV-V kategorije za temeljne trake nosača, do donje ivice podložnog betona. Rov širine 500 mm, dubine 950 mm, dužine 2600 mm. 4 nosača × 2 trake × 1,235 m3</t>
+          <t>Iskop zemlje/stijene IV-V kategorije za temeljne trake nosača, do donje ivice podložnog betona. Rov širine 500 mm, dubine 950 mm, dužine 2600 mm. 4 nosača × 2 trake × 1,235 m3. Rov se u stijeni siječe jednom širinom po cijeloj dubini; traka se betonira do zida rova, pa zatrpavanja nema.</t>
         </is>
       </c>
       <c r="C20" s="130" t="inlineStr">
@@ -1575,9 +1577,9 @@
           <t>2.2</t>
         </is>
       </c>
-      <c r="B21" s="132" t="inlineStr">
-        <is>
-          <t>Zatrpavanje preostalog dijela rova zemljom od iskopa uz nabijanje u slojevima. Traka je pune dubine, pa se zatrpava samo klin uz kosinu rova. 4 nosača × 2 trake × 0,117 m3</t>
+      <c r="B21" s="129" t="inlineStr">
+        <is>
+          <t>Odvoz i zbrinjavanje viška materijala od iskopa do deponije udaljene do 20 km. Traka i podložni beton ispunjavaju rov u cijelosti, pa se odvozi sav iskopani materijal. 4 nosača × 2 trake × 1,235 m3</t>
         </is>
       </c>
       <c r="C21" s="130" t="inlineStr">
@@ -1586,7 +1588,7 @@
         </is>
       </c>
       <c r="D21" s="130" t="n">
-        <v>0.9399999999999999</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="E21" s="131" t="n"/>
       <c r="F21" s="131">
@@ -1594,15 +1596,15 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="92">
+    <row r="22" ht="21.75" customHeight="1" s="92">
       <c r="A22" s="128" t="inlineStr">
         <is>
-          <t>2.2a</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="B22" s="129" t="inlineStr">
         <is>
-          <t>Odvoz i zbrinjavanje viška materijala od iskopa do deponije udaljene do 20 km.</t>
+          <t>Nabavka materijala, transport i ugradnja podložnog betona C12/15 ispod temeljnih traka, prema zahtjevima proizvođača. 4 nosača × 2 trake × 0,065 m3</t>
         </is>
       </c>
       <c r="C22" s="130" t="inlineStr">
@@ -1611,7 +1613,7 @@
         </is>
       </c>
       <c r="D22" s="130" t="n">
-        <v>8.94</v>
+        <v>0.52</v>
       </c>
       <c r="E22" s="131" t="n"/>
       <c r="F22" s="131">
@@ -1619,15 +1621,16 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="21.75" customHeight="1" s="92">
+    <row r="23" ht="105.75" customHeight="1" s="92">
       <c r="A23" s="128" t="inlineStr">
         <is>
-          <t>2.2b</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="B23" s="129" t="inlineStr">
         <is>
-          <t>Nabavka materijala, transport i ugradnja podložnog betona C12/15 ispod temeljnih traka, prema zahtjevima proizvođača. 4 nosača × 2 trake × 0,065 m3</t>
+          <t>Nabavka materijala, transport i betoniranje DVIJE temeljne trake po nosaču, betonom C30/37 klase izloženosti XC4 + XF3 prema BAS EN 206 (aerant 4–6 %, Dmax 16, konzistencija S3), uz upotrebu oplate i njegovanje betona. Armatura B500B, zaštitni sloj ≥50 mm, prema ovjerenom statičkom proračunu iz Tačke 1.3. Obračun po m³ ugrađenog betona. Traka 500 × 2600 mm, jedinstvene širine po cijeloj dubini (bez proširenja u dnu), PUNE dubine 900 mm = 1,170 m³ po traci. 4 nosača × 2 trake × 1,170 m³
+BETON I ARMATURA: beton klase C30/37, klase izloženosti XC4 + XF3 prema BAS EN 206, sa aerantom 4–6 %, Dmax 16, konzistencija S3; podložni beton C12/15 d=50 mm; armatura B500B, zaštitni sloj ≥50 mm. Klasa XF3 je mjerodavna zbog cikličnog smrzavanja i odmrzavanja u vlažnom stanju na 1076 m n.v. Temeljna spojnica mora biti ispod dubine smrzavanja za lokalitet, koju Ponuđač navodi u ponudi. Dubina 900 mm je tenderska osnova i mjerodavna je za ponudu; konačnu dubinu i armaturu potvrđuje ovjereni statički proračun iz Tačke 1.3. Traka se betonira punom dubinom rova i do zida rova — vlastita težina trake je dio dokaza sigurnosti na podizanje i prevrtanje. Temelj širi u dnu nego u vrhu tražio bi potkopavanje i u stijeni nije izvodiv, pa je presjek jedinstven.</t>
         </is>
       </c>
       <c r="C23" s="130" t="inlineStr">
@@ -1636,7 +1639,7 @@
         </is>
       </c>
       <c r="D23" s="130" t="n">
-        <v>0.52</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="E23" s="131" t="n"/>
       <c r="F23" s="131">
@@ -1644,215 +1647,192 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="105.75" customHeight="1" s="92">
+    <row r="24" ht="23.25" customHeight="1" s="92">
       <c r="A24" s="128" t="inlineStr">
         <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="B24" s="129" t="inlineStr">
-        <is>
-          <t>Nabavka materijala, transport i betoniranje DVIJE temeljne trake po nosaču, betonom C30/37 klase izloženosti XC4 + XF3 prema BAS EN 206 (aerant 4–6 %, Dmax 16, konzistencija S3), uz upotrebu oplate i njegovanje betona. Armatura B500B, zaštitni sloj ≥50 mm, prema ovjerenom statičkom proračunu iz Tačke 1.3. Obračun po m³ ugrađenog betona. Traka 400 mm (gore) / 500 mm (dolje) × 2600 mm, PUNE dubine 900 mm = 1,053 m³ po traci. 4 nosača × 2 trake × 1,053 m³
-BETON I ARMATURA: beton klase C30/37, klase izloženosti XC4 + XF3 prema BAS EN 206, sa aerantom 4–6 %, Dmax 16, konzistencija S3; podložni beton C12/15 d=50 mm; armatura B500B, zaštitni sloj ≥50 mm. Klasa XF3 je mjerodavna zbog cikličnog smrzavanja i odmrzavanja u vlažnom stanju na 1076 m n.v. Temeljna spojnica mora biti ispod dubine smrzavanja za lokalitet, koju Ponuđač navodi u ponudi. Dubina 900 mm je tenderska osnova i mjerodavna je za ponudu; konačnu dubinu i armaturu potvrđuje ovjereni statički proračun iz Tačke 1.3. Traka se betonira punom dubinom rova — vlastita težina trake je dio dokaza sigurnosti na podizanje i prevrtanje.</t>
-        </is>
-      </c>
-      <c r="C24" s="130" t="inlineStr">
-        <is>
-          <t>m3</t>
-        </is>
-      </c>
-      <c r="D24" s="130" t="n">
-        <v>8.42</v>
-      </c>
-      <c r="E24" s="131" t="n"/>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="B24" s="133" t="inlineStr">
+        <is>
+          <t>Obrada vidljivih strana i gornje površine temeljnih traka cementnim malterom u nagibu 1,0 %, zaglađeno do crnog sjaja. 0,50 × 2,60 × 8 traka = 10,4 m².</t>
+        </is>
+      </c>
+      <c r="C24" s="134" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="D24" s="134" t="n">
+        <v>10.4</v>
+      </c>
       <c r="F24" s="131">
         <f>IF(AND(D24&lt;&gt;"",E24&lt;&gt;""),D24*E24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="23.25" customHeight="1" s="92">
+    <row r="25" ht="15" customHeight="1" s="92">
       <c r="A25" s="128" t="inlineStr">
         <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="B25" s="133" t="inlineStr">
-        <is>
-          <t>Obrada vidljivih strana i gornje površine temeljnih traka cementnim malterom u nagibu 1,0 %, zaglađeno do crnog sjaja.</t>
-        </is>
-      </c>
-      <c r="C25" s="134" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="D25" s="134" t="n">
-        <v>12</v>
-      </c>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="B25" s="132" t="inlineStr">
+        <is>
+          <t>Ostali sitni građevinski i potrošni materijal.</t>
+        </is>
+      </c>
+      <c r="C25" s="130" t="inlineStr">
+        <is>
+          <t>paušal</t>
+        </is>
+      </c>
+      <c r="D25" s="130" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="131" t="n"/>
       <c r="F25" s="131">
         <f>IF(AND(D25&lt;&gt;"",E25&lt;&gt;""),D25*E25,"")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="92">
-      <c r="A26" s="128" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="B26" s="132" t="inlineStr">
-        <is>
-          <t>Ostali sitni građevinski i potrošni materijal.</t>
-        </is>
-      </c>
-      <c r="C26" s="130" t="inlineStr">
-        <is>
-          <t>paušal</t>
-        </is>
-      </c>
-      <c r="D26" s="130" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="131" t="n"/>
-      <c r="F26" s="131">
-        <f>IF(AND(D26&lt;&gt;"",E26&lt;&gt;""),D26*E26,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="92">
-      <c r="A27" s="135" t="n"/>
-      <c r="B27" s="135" t="inlineStr">
+      <c r="A26" s="135" t="n"/>
+      <c r="B26" s="135" t="inlineStr">
         <is>
           <t>UKUPNO 2 — GRAĐEVINSKI RADOVI ZA NOSAČE FN PANELA:</t>
         </is>
       </c>
-      <c r="C27" s="136" t="n"/>
-      <c r="D27" s="136" t="n"/>
-      <c r="E27" s="137" t="n"/>
-      <c r="F27" s="138">
-        <f>SUM(F20:F26)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1" s="92"/>
-    <row r="29" ht="15" customHeight="1" s="92">
-      <c r="A29" s="139" t="n"/>
-      <c r="B29" s="139" t="inlineStr">
+      <c r="C26" s="136" t="n"/>
+      <c r="D26" s="136" t="n"/>
+      <c r="E26" s="137" t="n"/>
+      <c r="F26" s="138">
+        <f>SUM(F20:F25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1" s="92"/>
+    <row r="28" ht="15" customHeight="1" s="92">
+      <c r="A28" s="139" t="n"/>
+      <c r="B28" s="139" t="inlineStr">
         <is>
           <t>UKUPNO LOT 1 — NOSAČI ZA FOTONAPONSKE PANELE (bez PDV-a):</t>
         </is>
       </c>
-      <c r="C29" s="136" t="n"/>
-      <c r="D29" s="137" t="n"/>
-      <c r="E29" s="137" t="n"/>
-      <c r="F29" s="140">
-        <f>F18+F27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="24" customHeight="1" s="92"/>
+      <c r="C28" s="136" t="n"/>
+      <c r="D28" s="137" t="n"/>
+      <c r="E28" s="137" t="n"/>
+      <c r="F28" s="140">
+        <f>F18+F26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1" s="92"/>
+    <row r="30" ht="36" customHeight="1" s="92">
+      <c r="A30" s="141" t="n"/>
+      <c r="B30" s="141" t="inlineStr">
+        <is>
+          <t>REKAPITULACIJA — LOT 1</t>
+        </is>
+      </c>
+      <c r="C30" s="122" t="n"/>
+      <c r="D30" s="122" t="n"/>
+      <c r="E30" s="142" t="n"/>
+      <c r="F30" s="143" t="n"/>
+    </row>
     <row r="31" ht="36" customHeight="1" s="92">
-      <c r="A31" s="141" t="n"/>
-      <c r="B31" s="141" t="inlineStr">
-        <is>
-          <t>REKAPITULACIJA — LOT 1</t>
+      <c r="A31" s="144" t="n"/>
+      <c r="B31" s="144" t="inlineStr">
+        <is>
+          <t>UKUPNO LOT 1 (bez PDV-a):</t>
         </is>
       </c>
       <c r="C31" s="122" t="n"/>
       <c r="D31" s="122" t="n"/>
       <c r="E31" s="142" t="n"/>
-      <c r="F31" s="143" t="n"/>
-    </row>
-    <row r="32" ht="36" customHeight="1" s="92">
+      <c r="F31" s="145">
+        <f>F28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1" s="92">
       <c r="A32" s="144" t="n"/>
       <c r="B32" s="144" t="inlineStr">
         <is>
-          <t>UKUPNO LOT 1 (bez PDV-a):</t>
+          <t>Popust (%):</t>
         </is>
       </c>
       <c r="C32" s="122" t="n"/>
       <c r="D32" s="122" t="n"/>
       <c r="E32" s="142" t="n"/>
-      <c r="F32" s="145">
-        <f>F29</f>
-        <v/>
-      </c>
+      <c r="F32" s="145" t="n"/>
     </row>
     <row r="33" ht="24" customHeight="1" s="92">
       <c r="A33" s="144" t="n"/>
       <c r="B33" s="144" t="inlineStr">
         <is>
-          <t>Popust (%):</t>
+          <t>UKUPNO LOT 1 sa popustom (bez PDV-a):</t>
         </is>
       </c>
       <c r="C33" s="122" t="n"/>
       <c r="D33" s="122" t="n"/>
       <c r="E33" s="142" t="n"/>
-      <c r="F33" s="145" t="n"/>
-    </row>
-    <row r="34" ht="24" customHeight="1" s="92">
+      <c r="F33" s="145">
+        <f>F31*(1-IF(F32="",0,F32/100))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="92">
       <c r="A34" s="144" t="n"/>
       <c r="B34" s="144" t="inlineStr">
         <is>
-          <t>UKUPNO LOT 1 sa popustom (bez PDV-a):</t>
+          <t>PDV 17%:</t>
         </is>
       </c>
       <c r="C34" s="122" t="n"/>
       <c r="D34" s="122" t="n"/>
       <c r="E34" s="142" t="n"/>
       <c r="F34" s="145">
-        <f>F32*(1-IF(F33="",0,F33/100))</f>
+        <f>F33*0.17</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="92">
-      <c r="A35" s="144" t="n"/>
-      <c r="B35" s="144" t="inlineStr">
-        <is>
-          <t>PDV 17%:</t>
+      <c r="A35" s="141" t="n"/>
+      <c r="B35" s="141" t="inlineStr">
+        <is>
+          <t>UKUPNO LOT 1 sa PDV-om:</t>
         </is>
       </c>
       <c r="C35" s="122" t="n"/>
       <c r="D35" s="122" t="n"/>
       <c r="E35" s="142" t="n"/>
-      <c r="F35" s="145">
-        <f>F34*0.17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="92">
-      <c r="A36" s="141" t="n"/>
-      <c r="B36" s="141" t="inlineStr">
-        <is>
-          <t>UKUPNO LOT 1 sa PDV-om:</t>
-        </is>
-      </c>
-      <c r="C36" s="122" t="n"/>
-      <c r="D36" s="122" t="n"/>
-      <c r="E36" s="142" t="n"/>
-      <c r="F36" s="143">
-        <f>F34+F35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37"/>
+      <c r="F35" s="143">
+        <f>F33+F34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37" ht="24" customHeight="1" s="92"/>
     <row r="38" ht="24" customHeight="1" s="92"/>
-    <row r="39" ht="24" customHeight="1" s="92"/>
-    <row r="40"/>
-    <row r="41" ht="24" customHeight="1" s="92"/>
-    <row r="42" ht="156" customHeight="1" s="92"/>
-    <row r="43" ht="24" customHeight="1" s="92"/>
+    <row r="39"/>
+    <row r="40" ht="24" customHeight="1" s="92"/>
+    <row r="41" ht="156" customHeight="1" s="92"/>
+    <row r="42" ht="24" customHeight="1" s="92"/>
+    <row r="43"/>
     <row r="44"/>
     <row r="45"/>
-    <row r="46"/>
-    <row r="47" ht="15" customHeight="1" s="92">
-      <c r="A47" s="91" t="n"/>
-    </row>
-    <row r="48"/>
-    <row r="49" ht="15" customHeight="1" s="92">
-      <c r="A49" s="91" t="n"/>
-    </row>
-    <row r="50"/>
+    <row r="46" ht="15" customHeight="1" s="92">
+      <c r="A46" s="91" t="n"/>
+    </row>
+    <row r="47"/>
+    <row r="48" ht="15" customHeight="1" s="92">
+      <c r="A48" s="91" t="n"/>
+    </row>
+    <row r="49"/>
+    <row r="50" ht="15" customHeight="1" s="92">
+      <c r="A50" s="91" t="n"/>
+    </row>
     <row r="51" ht="15" customHeight="1" s="92">
       <c r="A51" s="91" t="n"/>
     </row>
@@ -1862,69 +1842,66 @@
     <row r="53" ht="15" customHeight="1" s="92">
       <c r="A53" s="91" t="n"/>
     </row>
-    <row r="54" ht="15" customHeight="1" s="92">
+    <row r="54" ht="24" customHeight="1" s="92">
       <c r="A54" s="91" t="n"/>
     </row>
-    <row r="55" ht="24" customHeight="1" s="92">
-      <c r="A55" s="91" t="n"/>
-    </row>
-    <row r="57" ht="24" customHeight="1" s="92"/>
+    <row r="56" ht="24" customHeight="1" s="92"/>
+    <row r="80" ht="24" customHeight="1" s="92"/>
     <row r="81" ht="24" customHeight="1" s="92"/>
-    <row r="82" ht="24" customHeight="1" s="92"/>
-    <row r="84" ht="24" customHeight="1" s="92"/>
-    <row r="88" ht="24" customHeight="1" s="92"/>
-    <row r="89" ht="36" customHeight="1" s="92"/>
+    <row r="83" ht="24" customHeight="1" s="92"/>
+    <row r="87" ht="24" customHeight="1" s="92"/>
+    <row r="88" ht="36" customHeight="1" s="92"/>
+    <row r="98" ht="24" customHeight="1" s="92"/>
     <row r="99" ht="24" customHeight="1" s="92"/>
     <row r="100" ht="24" customHeight="1" s="92"/>
-    <row r="101" ht="24" customHeight="1" s="92"/>
+    <row r="104" ht="24" customHeight="1" s="92"/>
     <row r="105" ht="24" customHeight="1" s="92"/>
-    <row r="106" ht="24" customHeight="1" s="92"/>
-    <row r="108" ht="24" customHeight="1" s="92"/>
-    <row r="110" ht="24" customHeight="1" s="92"/>
-    <row r="112" ht="24" customHeight="1" s="92"/>
-    <row r="115" ht="36" customHeight="1" s="92"/>
-    <row r="116" ht="24" customHeight="1" s="92"/>
-    <row r="117" ht="84" customHeight="1" s="92"/>
+    <row r="107" ht="24" customHeight="1" s="92"/>
+    <row r="109" ht="24" customHeight="1" s="92"/>
+    <row r="111" ht="24" customHeight="1" s="92"/>
+    <row r="114" ht="36" customHeight="1" s="92"/>
+    <row r="115" ht="24" customHeight="1" s="92"/>
+    <row r="116" ht="84" customHeight="1" s="92"/>
+    <row r="117" ht="24" customHeight="1" s="92"/>
     <row r="118" ht="24" customHeight="1" s="92"/>
     <row r="119" ht="24" customHeight="1" s="92"/>
     <row r="120" ht="24" customHeight="1" s="92"/>
-    <row r="121" ht="24" customHeight="1" s="92"/>
-    <row r="122" ht="48" customHeight="1" s="92"/>
-    <row r="124" ht="36" customHeight="1" s="92"/>
+    <row r="121" ht="48" customHeight="1" s="92"/>
+    <row r="123" ht="36" customHeight="1" s="92"/>
+    <row r="125" ht="24" customHeight="1" s="92"/>
     <row r="126" ht="24" customHeight="1" s="92"/>
-    <row r="127" ht="24" customHeight="1" s="92"/>
-    <row r="128" ht="48" customHeight="1" s="92"/>
-    <row r="129" ht="24" customHeight="1" s="92"/>
-    <row r="131" ht="36" customHeight="1" s="92"/>
+    <row r="127" ht="48" customHeight="1" s="92"/>
+    <row r="128" ht="24" customHeight="1" s="92"/>
+    <row r="130" ht="36" customHeight="1" s="92"/>
+    <row r="134" ht="24" customHeight="1" s="92"/>
     <row r="135" ht="24" customHeight="1" s="92"/>
-    <row r="136" ht="24" customHeight="1" s="92"/>
-    <row r="137" ht="36" customHeight="1" s="92"/>
-    <row r="138" ht="24" customHeight="1" s="92"/>
+    <row r="136" ht="36" customHeight="1" s="92"/>
+    <row r="137" ht="24" customHeight="1" s="92"/>
+    <row r="142" ht="36" customHeight="1" s="92"/>
     <row r="143" ht="36" customHeight="1" s="92"/>
     <row r="144" ht="36" customHeight="1" s="92"/>
-    <row r="145" ht="36" customHeight="1" s="92"/>
+    <row r="146" ht="24" customHeight="1" s="92"/>
     <row r="147" ht="24" customHeight="1" s="92"/>
-    <row r="148" ht="24" customHeight="1" s="92"/>
-    <row r="150" ht="24" customHeight="1" s="92"/>
-    <row r="156" ht="48" customHeight="1" s="92"/>
-    <row r="157" ht="24" customHeight="1" s="92"/>
-    <row r="158" ht="48" customHeight="1" s="92"/>
-    <row r="163" ht="36" customHeight="1" s="92"/>
-    <row r="164" ht="24" customHeight="1" s="92"/>
-    <row r="165" ht="36" customHeight="1" s="92"/>
-    <row r="167" ht="24" customHeight="1" s="92"/>
+    <row r="149" ht="24" customHeight="1" s="92"/>
+    <row r="155" ht="48" customHeight="1" s="92"/>
+    <row r="156" ht="24" customHeight="1" s="92"/>
+    <row r="157" ht="48" customHeight="1" s="92"/>
+    <row r="162" ht="36" customHeight="1" s="92"/>
+    <row r="163" ht="24" customHeight="1" s="92"/>
+    <row r="164" ht="36" customHeight="1" s="92"/>
+    <row r="166" ht="24" customHeight="1" s="92"/>
+    <row r="1048574" ht="12.75" customHeight="1" s="92"/>
     <row r="1048575" ht="12.75" customHeight="1" s="92"/>
-    <row r="1048576" ht="12.75" customHeight="1" s="92"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A53:E53"/>
     <mergeCell ref="A54:E54"/>
     <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A53:E53"/>
     <mergeCell ref="A51:E51"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A48:D48"/>
     <mergeCell ref="A3:F3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
